--- a/tests/testthat/fixtures/summary.xlsx
+++ b/tests/testthat/fixtures/summary.xlsx
@@ -7,7 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="1" r:id="rId1"/>
+    <sheet name="Portfolio" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -340,6 +341,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Synthetic summary notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
